--- a/templates/Sales Contract Template.xlsx
+++ b/templates/Sales Contract Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ys-project\auto-contact-desktop\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ys-project\Auto-Contract\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56760FBA-7D12-47CB-9BA6-D45587D565DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC48ABA9-01F7-4E36-AA7D-11437CC4FCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="165">
   <si>
     <t>Series No.
 序号</t>
@@ -606,9 +606,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{{total_amount}}</t>
-  </si>
-  <si>
     <t>Total Amount：${{total_amount}} (in words: {{total_amount_words_en}})</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -729,14 +726,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{{unit_price}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{total_amount}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>ADD: {{seller_address}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -758,6 +747,14 @@
   </si>
   <si>
     <t>EMAIL: {{buyer_email}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>${{unit_price}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>${{total_amount}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2286,8 +2283,8 @@
     <col min="2" max="2" width="7.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="23.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.875" style="2" customWidth="1"/>
@@ -2502,16 +2499,16 @@
         <v>126</v>
       </c>
       <c r="E17" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="F17" s="33" t="s">
-        <v>157</v>
-      </c>
       <c r="G17" s="34" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H17" s="36" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -2528,7 +2525,7 @@
     </row>
     <row r="19" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B19" s="53"/>
       <c r="C19" s="53"/>
@@ -2537,13 +2534,13 @@
       <c r="F19" s="53"/>
       <c r="G19" s="53"/>
       <c r="H19" s="37" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="I19" s="18"/>
     </row>
     <row r="20" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="74" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B20" s="75"/>
       <c r="C20" s="75"/>
@@ -2563,7 +2560,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G21" s="20"/>
       <c r="H21" s="20"/>
@@ -2576,7 +2573,7 @@
       <c r="C22" s="13"/>
       <c r="E22" s="20"/>
       <c r="F22" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="20"/>
@@ -2610,7 +2607,7 @@
     </row>
     <row r="26" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B26" s="53"/>
       <c r="C26" s="53"/>
@@ -2623,7 +2620,7 @@
     </row>
     <row r="27" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="53" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B27" s="53"/>
       <c r="C27" s="53"/>
@@ -2645,7 +2642,7 @@
     </row>
     <row r="29" spans="1:11" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B29" s="53"/>
       <c r="C29" s="53"/>
@@ -2657,7 +2654,7 @@
     </row>
     <row r="30" spans="1:11" s="1" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B30" s="53"/>
       <c r="C30" s="53"/>
@@ -2669,7 +2666,7 @@
     </row>
     <row r="31" spans="1:11" s="1" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="64" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B31" s="64"/>
       <c r="C31" s="64"/>
@@ -2682,7 +2679,7 @@
     </row>
     <row r="32" spans="1:11" s="1" customFormat="1" ht="59.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B32" s="64"/>
       <c r="C32" s="64"/>
@@ -2694,7 +2691,7 @@
     </row>
     <row r="33" spans="1:8" s="1" customFormat="1" ht="44.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B33" s="64"/>
       <c r="C33" s="64"/>
@@ -2706,7 +2703,7 @@
     </row>
     <row r="34" spans="1:8" s="1" customFormat="1" ht="30.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="64" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B34" s="64"/>
       <c r="C34" s="64"/>
@@ -2718,7 +2715,7 @@
     </row>
     <row r="35" spans="1:8" s="1" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B35" s="64"/>
       <c r="C35" s="64"/>
@@ -2730,7 +2727,7 @@
     </row>
     <row r="36" spans="1:8" s="1" customFormat="1" ht="30.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="64" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B36" s="64"/>
       <c r="C36" s="64"/>
@@ -2742,7 +2739,7 @@
     </row>
     <row r="37" spans="1:8" s="1" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="64" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="64"/>
       <c r="C37" s="64"/>
@@ -2754,7 +2751,7 @@
     </row>
     <row r="38" spans="1:8" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="64"/>
       <c r="C38" s="64"/>
@@ -2766,7 +2763,7 @@
     </row>
     <row r="39" spans="1:8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="64"/>
       <c r="C39" s="64"/>
@@ -2778,7 +2775,7 @@
     </row>
     <row r="40" spans="1:8" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B40" s="64"/>
       <c r="C40" s="64"/>
@@ -2799,7 +2796,7 @@
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D42" s="57" t="s">
         <v>84</v>
@@ -2818,10 +2815,10 @@
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44" s="57" t="s">
         <v>146</v>
-      </c>
-      <c r="D44" s="57" t="s">
-        <v>147</v>
       </c>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
@@ -2837,10 +2834,10 @@
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" s="57" t="s">
         <v>148</v>
-      </c>
-      <c r="D46" s="57" t="s">
-        <v>149</v>
       </c>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
@@ -2856,7 +2853,7 @@
     </row>
     <row r="48" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="65" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B48" s="65"/>
       <c r="C48" s="65"/>
@@ -2868,7 +2865,7 @@
     </row>
     <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B49" s="57"/>
       <c r="C49" s="57"/>
@@ -2906,7 +2903,7 @@
     </row>
     <row r="53" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B53" s="57"/>
       <c r="C53" s="57"/>
@@ -3217,13 +3214,13 @@
     </row>
     <row r="85" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="59" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B85" s="59"/>
       <c r="C85" s="59"/>
       <c r="D85" s="59"/>
       <c r="E85" s="61" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F85" s="62"/>
       <c r="G85" s="62"/>
@@ -3231,13 +3228,13 @@
     </row>
     <row r="86" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="60" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B86" s="60"/>
       <c r="C86" s="60"/>
       <c r="D86" s="60"/>
       <c r="E86" s="61" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F86" s="62"/>
       <c r="G86" s="62"/>
@@ -3245,13 +3242,13 @@
     </row>
     <row r="87" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="60" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B87" s="60"/>
       <c r="C87" s="60"/>
       <c r="D87" s="60"/>
       <c r="E87" s="61" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F87" s="62"/>
       <c r="G87" s="62"/>
@@ -3337,7 +3334,7 @@
     </row>
     <row r="95" spans="1:8" ht="111" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B95" s="46"/>
       <c r="C95" s="46"/>
@@ -3540,7 +3537,7 @@
         <v>72</v>
       </c>
       <c r="B111" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C111" s="27"/>
       <c r="D111" s="28"/>
@@ -3548,7 +3545,7 @@
         <v>72</v>
       </c>
       <c r="F111" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G111" s="27"/>
       <c r="H111" s="28"/>
